--- a/data/trans_bre/P2C_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 16,24</t>
+          <t>-5,96; 16,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 8,69</t>
+          <t>-9,61; 9,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 4,27</t>
+          <t>-19,14; 3,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 6,94</t>
+          <t>-13,04; 7,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 25,33</t>
+          <t>-7,84; 26,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 10,48</t>
+          <t>-10,36; 11,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 5,07</t>
+          <t>-21,78; 4,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 32,96</t>
+          <t>-40,52; 36,91</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 9,91</t>
+          <t>-15,23; 9,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 1,83</t>
+          <t>-10,03; 2,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 10,23</t>
+          <t>-12,07; 10,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 13,69</t>
+          <t>-8,9; 15,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 13,71</t>
+          <t>-18,6; 12,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 1,91</t>
+          <t>-10,12; 2,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 14,86</t>
+          <t>-14,98; 15,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 60,4</t>
+          <t>-26,63; 68,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 5,3</t>
+          <t>-20,93; 5,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 13,26</t>
+          <t>-5,51; 13,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 15,35</t>
+          <t>-14,02; 14,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 17,97</t>
+          <t>-12,39; 18,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 8,74</t>
+          <t>-29,33; 8,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 16,94</t>
+          <t>-6,07; 17,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 24,55</t>
+          <t>-18,4; 23,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 71,69</t>
+          <t>-33,92; 75,9</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 5,79</t>
+          <t>-11,45; 6,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 9,6</t>
+          <t>-2,92; 8,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 6,51</t>
+          <t>-10,03; 5,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 5,42</t>
+          <t>-13,9; 5,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 9,42</t>
+          <t>-15,79; 9,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 11,69</t>
+          <t>-3,28; 10,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 8,85</t>
+          <t>-12,36; 8,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 21,63</t>
+          <t>-43,72; 19,66</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 15,49</t>
+          <t>-8,11; 15,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 2,63</t>
+          <t>-9,66; 3,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 8,13</t>
+          <t>-10,43; 8,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 3,28</t>
+          <t>-21,24; 3,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 24,35</t>
+          <t>-11,0; 25,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 2,88</t>
+          <t>-10,24; 3,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 11,32</t>
+          <t>-12,39; 11,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 10,35</t>
+          <t>-44,67; 9,75</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 21,8</t>
+          <t>-3,79; 21,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 22,3</t>
+          <t>3,28; 22,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 6,3</t>
+          <t>-22,66; 5,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 6,48</t>
+          <t>-21,98; 5,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 40,25</t>
+          <t>-5,51; 40,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 31,15</t>
+          <t>3,88; 32,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 10,3</t>
+          <t>-30,62; 8,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 14,56</t>
+          <t>-40,85; 14,86</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 5,02</t>
+          <t>-4,0; 5,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,02</t>
+          <t>-1,17; 5,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,21</t>
+          <t>-6,87; 1,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 1,51</t>
+          <t>-9,2; 1,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 7,55</t>
+          <t>-5,65; 8,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,79</t>
+          <t>-1,28; 6,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 3,04</t>
+          <t>-8,76; 2,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 4,9</t>
+          <t>-25,67; 4,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 16,95</t>
+          <t>-6,92; 16,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 9,07</t>
+          <t>-9,35; 8,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 3,79</t>
+          <t>-17,91; 5,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 7,71</t>
+          <t>-12,6; 6,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 26,34</t>
+          <t>-8,94; 25,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 11,0</t>
+          <t>-10,42; 10,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 4,59</t>
+          <t>-21,03; 7,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 36,91</t>
+          <t>-40,67; 30,39</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 9,09</t>
+          <t>-16,01; 8,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 2,0</t>
+          <t>-9,13; 2,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 10,28</t>
+          <t>-11,86; 9,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 15,04</t>
+          <t>-7,9; 15,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 12,75</t>
+          <t>-19,28; 12,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 2,08</t>
+          <t>-9,31; 2,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 15,27</t>
+          <t>-15,19; 13,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 68,58</t>
+          <t>-23,04; 75,76</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 5,68</t>
+          <t>-19,6; 8,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 13,48</t>
+          <t>-4,76; 14,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 14,65</t>
+          <t>-14,47; 14,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 18,55</t>
+          <t>-14,09; 19,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 8,75</t>
+          <t>-27,43; 13,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 17,54</t>
+          <t>-5,27; 18,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 23,61</t>
+          <t>-19,18; 24,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 75,9</t>
+          <t>-38,23; 84,57</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 6,27</t>
+          <t>-11,06; 6,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 8,9</t>
+          <t>-2,97; 8,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 5,96</t>
+          <t>-9,25; 6,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 5,59</t>
+          <t>-13,7; 5,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 9,87</t>
+          <t>-15,11; 9,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 10,8</t>
+          <t>-3,24; 10,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 8,16</t>
+          <t>-11,33; 8,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 19,66</t>
+          <t>-43,85; 20,02</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 15,5</t>
+          <t>-8,68; 14,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 3,37</t>
+          <t>-9,11; 4,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 8,65</t>
+          <t>-11,07; 7,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 3,49</t>
+          <t>-21,36; 2,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 25,6</t>
+          <t>-11,96; 23,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 3,64</t>
+          <t>-9,64; 4,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 11,91</t>
+          <t>-13,34; 11,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,67; 9,75</t>
+          <t>-43,11; 10,27</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 21,6</t>
+          <t>-3,92; 21,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 22,69</t>
+          <t>1,33; 21,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 5,67</t>
+          <t>-21,52; 6,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 5,96</t>
+          <t>-23,3; 7,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 40,16</t>
+          <t>-5,82; 38,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 32,07</t>
+          <t>1,97; 30,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 8,98</t>
+          <t>-29,72; 10,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 14,86</t>
+          <t>-41,73; 19,16</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 5,6</t>
+          <t>-4,13; 5,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,41</t>
+          <t>-1,06; 5,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,66</t>
+          <t>-6,87; 1,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 1,35</t>
+          <t>-9,97; 1,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 8,5</t>
+          <t>-5,69; 8,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 6,34</t>
+          <t>-1,2; 6,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 2,32</t>
+          <t>-8,72; 2,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 4,61</t>
+          <t>-27,88; 4,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-4,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,61%</t>
+          <t>-14,95%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 16,28</t>
+          <t>-6,51; 16,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 8,89</t>
+          <t>-9,24; 8,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 5,48</t>
+          <t>-19,79; 4,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 6,69</t>
+          <t>-14,72; 5,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 25,37</t>
+          <t>-7,74; 25,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 10,47</t>
+          <t>-10,06; 10,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 7,15</t>
+          <t>-23,02; 5,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 30,39</t>
+          <t>-42,51; 23,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 8,75</t>
+          <t>-14,64; 9,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 2,03</t>
+          <t>-9,39; 1,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 9,48</t>
+          <t>-12,25; 10,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 15,16</t>
+          <t>-8,88; 13,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 12,61</t>
+          <t>-18,38; 13,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 2,11</t>
+          <t>-9,59; 1,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 13,65</t>
+          <t>-15,41; 14,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 75,76</t>
+          <t>-27,03; 61,27</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 8,39</t>
+          <t>-18,48; 5,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 14,43</t>
+          <t>-5,57; 13,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 14,51</t>
+          <t>-13,44; 15,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 19,18</t>
+          <t>-11,82; 19,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 13,53</t>
+          <t>-25,12; 8,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 18,78</t>
+          <t>-6,38; 16,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 24,03</t>
+          <t>-17,66; 24,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 84,57</t>
+          <t>-33,57; 78,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-13,24%</t>
+          <t>-8,04%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 6,29</t>
+          <t>-11,94; 5,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 8,31</t>
+          <t>-3,45; 9,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 6,31</t>
+          <t>-8,42; 6,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 5,45</t>
+          <t>-9,99; 5,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 9,93</t>
+          <t>-16,2; 9,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 10,04</t>
+          <t>-3,83; 11,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 8,76</t>
+          <t>-10,74; 8,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,85; 20,02</t>
+          <t>-30,38; 21,2</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,54</t>
+          <t>-6,36</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,34%</t>
+          <t>-15,27%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 14,68</t>
+          <t>-8,32; 15,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 4,28</t>
+          <t>-10,26; 2,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 7,99</t>
+          <t>-11,33; 8,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 2,87</t>
+          <t>-19,44; 4,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 23,18</t>
+          <t>-11,33; 24,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 4,85</t>
+          <t>-10,8; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 11,1</t>
+          <t>-13,47; 11,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,11; 10,27</t>
+          <t>-38,44; 12,81</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,79</t>
+          <t>-11,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-16,24%</t>
+          <t>-23,67%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 21,14</t>
+          <t>-3,17; 21,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 21,99</t>
+          <t>2,81; 22,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 6,39</t>
+          <t>-22,03; 6,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 7,47</t>
+          <t>-28,46; 2,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 38,11</t>
+          <t>-4,57; 40,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 30,65</t>
+          <t>3,44; 31,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 10,34</t>
+          <t>-30,86; 10,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 19,16</t>
+          <t>-49,32; 5,85</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-10,66%</t>
+          <t>-9,44%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 5,69</t>
+          <t>-3,81; 5,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,38</t>
+          <t>-1,39; 5,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,97</t>
+          <t>-7,02; 2,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 1,27</t>
+          <t>-8,84; 1,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 8,53</t>
+          <t>-5,43; 7,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 6,27</t>
+          <t>-1,55; 5,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 2,73</t>
+          <t>-9,03; 3,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 4,16</t>
+          <t>-24,04; 3,76</t>
         </is>
       </c>
     </row>
